--- a/data/trans_camb/P16A01-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P16A01-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,87; 7,8</t>
+          <t>1,86; 7,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 3,3</t>
+          <t>-1,92; 3,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 3,09</t>
+          <t>-1,82; 3,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,15; 7,1</t>
+          <t>1,8; 7,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,97; 7,03</t>
+          <t>1,99; 7,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 4,34</t>
+          <t>0,14; 4,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,57; 6,51</t>
+          <t>2,67; 6,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,35</t>
+          <t>0,79; 4,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 3,04</t>
+          <t>-0,18; 2,95</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,04; 193,99</t>
+          <t>24,58; 175,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-28,0; 82,22</t>
+          <t>-29,12; 72,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-29,66; 76,16</t>
+          <t>-28,68; 78,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41,87; 238,94</t>
+          <t>34,09; 222,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>37,98; 241,74</t>
+          <t>35,33; 235,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,28; 144,24</t>
+          <t>2,87; 163,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,05; 167,45</t>
+          <t>46,5; 162,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,82; 110,11</t>
+          <t>14,11; 113,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 78,92</t>
+          <t>-3,39; 73,14</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 1,86</t>
+          <t>-3,01; 2,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 2,97</t>
+          <t>-1,86; 3,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 1,12</t>
+          <t>-5,81; 1,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 4,04</t>
+          <t>-0,86; 3,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 4,86</t>
+          <t>0,02; 5,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 5,18</t>
+          <t>0,63; 5,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 2,28</t>
+          <t>-1,16; 2,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 3,25</t>
+          <t>-0,18; 3,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 2,39</t>
+          <t>-2,45; 2,35</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-34,4; 29,07</t>
+          <t>-33,6; 31,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-23,34; 46,96</t>
+          <t>-20,61; 46,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-61,33; 15,49</t>
+          <t>-63,07; 16,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,98; 80,48</t>
+          <t>-11,53; 79,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 99,16</t>
+          <t>-1,64; 98,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,25; 110,48</t>
+          <t>7,18; 108,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-14,95; 39,41</t>
+          <t>-15,16; 36,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 54,44</t>
+          <t>-2,4; 51,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-29,9; 39,02</t>
+          <t>-30,63; 36,27</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 7,16</t>
+          <t>0,5; 7,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 2,51</t>
+          <t>-2,95; 2,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 2,62</t>
+          <t>-3,37; 2,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 4,09</t>
+          <t>-1,75; 4,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 3,23</t>
+          <t>-2,14; 3,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 0,53</t>
+          <t>-5,14; 0,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 4,7</t>
+          <t>0,55; 4,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 2,05</t>
+          <t>-1,6; 2,05</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 0,36</t>
+          <t>-3,85; 0,58</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,09; 124,92</t>
+          <t>5,05; 120,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-34,61; 46,27</t>
+          <t>-35,29; 47,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-39,66; 47,11</t>
+          <t>-39,28; 41,5</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-17,1; 80,05</t>
+          <t>-21,65; 77,49</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-27,53; 62,75</t>
+          <t>-27,17; 68,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-72,68; 5,4</t>
+          <t>-66,94; 12,78</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,15; 79,68</t>
+          <t>6,72; 79,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-22,19; 34,71</t>
+          <t>-20,79; 36,02</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-52,03; 7,43</t>
+          <t>-50,84; 8,33</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,3; 5,71</t>
+          <t>0,49; 5,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 4,22</t>
+          <t>-0,64; 4,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 3,48</t>
+          <t>-1,82; 3,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 3,44</t>
+          <t>-1,78; 3,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 3,64</t>
+          <t>-1,75; 3,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 2,44</t>
+          <t>-2,75; 2,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 3,58</t>
+          <t>0,19; 3,84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 3,04</t>
+          <t>-0,26; 3,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 2,14</t>
+          <t>-1,36; 2,18</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,18; 88,09</t>
+          <t>5,54; 91,76</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 68,04</t>
+          <t>-7,71; 70,71</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-20,21; 55,16</t>
+          <t>-23,56; 55,52</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-17,05; 47,94</t>
+          <t>-18,58; 47,84</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-14,49; 51,97</t>
+          <t>-18,19; 48,12</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-25,17; 34,63</t>
+          <t>-28,4; 29,43</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 50,57</t>
+          <t>1,76; 54,73</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 43,87</t>
+          <t>-2,83; 45,15</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-16,53; 32,34</t>
+          <t>-15,79; 31,5</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,97</t>
+          <t>1,16; 3,85</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 2,22</t>
+          <t>-0,63; 2,02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 1,11</t>
+          <t>-1,98; 1,09</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,29</t>
+          <t>0,64; 3,18</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,18</t>
+          <t>0,65; 3,37</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 2,04</t>
+          <t>-0,72; 1,91</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,08</t>
+          <t>1,28; 3,1</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,22</t>
+          <t>0,4; 2,35</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,33</t>
+          <t>-0,75; 1,31</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>15,76; 61,9</t>
+          <t>15,9; 61,55</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 36,0</t>
+          <t>-7,9; 32,24</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-27,63; 17,16</t>
+          <t>-27,16; 16,71</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9,78; 56,37</t>
+          <t>8,64; 53,27</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>6,59; 54,88</t>
+          <t>9,37; 58,99</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-13,07; 34,57</t>
+          <t>-10,29; 31,79</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,82; 48,01</t>
+          <t>17,66; 50,05</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>6,53; 35,43</t>
+          <t>5,51; 37,07</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-11,31; 21,44</t>
+          <t>-10,58; 20,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A01-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P16A01-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,33</t>
+          <t>2,36</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,46</t>
+          <t>1,47</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 7,53</t>
+          <t>1,89; 7,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 3,0</t>
+          <t>-2,1; 2,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 3,26</t>
+          <t>-1,9; 3,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 7,14</t>
+          <t>2,02; 7,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,99; 7,19</t>
+          <t>1,69; 6,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 4,45</t>
+          <t>0,14; 4,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,67; 6,39</t>
+          <t>2,46; 6,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 4,42</t>
+          <t>0,79; 4,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 2,95</t>
+          <t>-0,21; 2,91</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,21%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,58; 175,33</t>
+          <t>25,04; 177,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-29,12; 72,57</t>
+          <t>-32,2; 65,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-28,68; 78,53</t>
+          <t>-30,28; 73,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34,09; 222,57</t>
+          <t>32,3; 241,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,33; 235,83</t>
+          <t>28,78; 221,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,87; 163,68</t>
+          <t>2,34; 141,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,5; 162,44</t>
+          <t>45,92; 163,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,11; 113,76</t>
+          <t>13,4; 111,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 73,14</t>
+          <t>-4,95; 73,34</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-1,7</t>
+          <t>-0,18</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,92</t>
+          <t>2,56</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>1,2</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 2,06</t>
+          <t>-2,77; 2,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 3,12</t>
+          <t>-2,03; 3,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 1,12</t>
+          <t>-2,9; 2,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 3,96</t>
+          <t>-0,83; 3,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,02; 5,07</t>
+          <t>-0,14; 4,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 5,33</t>
+          <t>0,5; 4,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 2,29</t>
+          <t>-1,16; 2,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 3,17</t>
+          <t>-0,29; 3,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 2,35</t>
+          <t>-0,66; 2,85</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-21,75%</t>
+          <t>-2,28%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>17,36%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-33,6; 31,1</t>
+          <t>-31,57; 31,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-20,61; 46,25</t>
+          <t>-20,86; 47,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-63,07; 16,26</t>
+          <t>-33,46; 35,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,53; 79,99</t>
+          <t>-11,7; 84,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 98,64</t>
+          <t>-2,6; 89,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,18; 108,72</t>
+          <t>6,67; 102,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-15,16; 36,94</t>
+          <t>-15,18; 39,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 51,45</t>
+          <t>-4,12; 50,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-30,63; 36,27</t>
+          <t>-8,22; 46,77</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,51</t>
+          <t>-0,62</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,02</t>
+          <t>-0,24</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,4</t>
+          <t>-0,43</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,5; 7,17</t>
+          <t>0,81; 7,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 2,53</t>
+          <t>-2,91; 2,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 2,32</t>
+          <t>-3,44; 2,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 4,03</t>
+          <t>-1,51; 4,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 3,29</t>
+          <t>-2,13; 3,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 0,75</t>
+          <t>-2,91; 2,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 4,52</t>
+          <t>0,47; 4,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 2,05</t>
+          <t>-1,63; 2,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 0,58</t>
+          <t>-2,47; 1,48</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-7,34%</t>
+          <t>-8,87%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-30,95%</t>
+          <t>-3,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-20,76%</t>
+          <t>-6,35%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,05; 120,69</t>
+          <t>8,75; 127,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-35,29; 47,1</t>
+          <t>-34,33; 44,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-39,28; 41,5</t>
+          <t>-40,43; 40,79</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-21,65; 77,49</t>
+          <t>-19,15; 82,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-27,17; 68,26</t>
+          <t>-27,68; 63,2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-66,94; 12,78</t>
+          <t>-36,39; 37,39</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,72; 79,0</t>
+          <t>6,22; 84,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-20,79; 36,02</t>
+          <t>-21,34; 39,34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-50,84; 8,33</t>
+          <t>-32,14; 24,9</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>1,13</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,01</t>
+          <t>0,51</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>0,8</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,49; 5,49</t>
+          <t>0,34; 5,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 4,28</t>
+          <t>-0,74; 4,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 3,38</t>
+          <t>-1,39; 3,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 3,28</t>
+          <t>-1,5; 3,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 3,33</t>
+          <t>-1,53; 3,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 2,22</t>
+          <t>-1,7; 2,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,19; 3,84</t>
+          <t>0,2; 3,86</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 3,1</t>
+          <t>-0,4; 3,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 2,18</t>
+          <t>-0,92; 2,49</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,54; 91,76</t>
+          <t>3,2; 100,37</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 70,71</t>
+          <t>-9,31; 69,1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-23,56; 55,52</t>
+          <t>-17,82; 60,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-18,58; 47,84</t>
+          <t>-16,27; 45,03</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-18,19; 48,12</t>
+          <t>-16,05; 49,29</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-28,4; 29,43</t>
+          <t>-17,11; 37,39</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,76; 54,73</t>
+          <t>1,87; 55,79</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 45,15</t>
+          <t>-4,37; 45,56</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-15,79; 31,5</t>
+          <t>-11,04; 35,68</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,31</t>
+          <t>0,26</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,73</t>
+          <t>1,3</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>0,79</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,85</t>
+          <t>1,09; 3,9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 2,02</t>
+          <t>-0,53; 2,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 1,09</t>
+          <t>-1,04; 1,67</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,18</t>
+          <t>0,5; 3,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,37</t>
+          <t>0,62; 3,27</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 1,91</t>
+          <t>0,07; 2,47</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,1</t>
+          <t>1,27; 3,09</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,35</t>
+          <t>0,48; 2,24</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,31</t>
+          <t>-0,06; 1,67</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-4,5%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>15,9; 61,55</t>
+          <t>14,49; 62,05</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 32,24</t>
+          <t>-7,15; 33,99</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-27,16; 16,71</t>
+          <t>-14,12; 26,72</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8,64; 53,27</t>
+          <t>7,16; 54,85</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>9,37; 58,99</t>
+          <t>8,7; 56,66</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-10,29; 31,79</t>
+          <t>1,3; 44,14</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,66; 50,05</t>
+          <t>17,75; 49,18</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>5,51; 37,07</t>
+          <t>6,72; 35,94</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 20,97</t>
+          <t>-0,77; 26,99</t>
         </is>
       </c>
     </row>
